--- a/results/prediction_result.xlsx
+++ b/results/prediction_result.xlsx
@@ -490,64 +490,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17977.70078277588</v>
+        <v>3653.258806228638</v>
       </c>
       <c r="E2" t="n">
-        <v>17.97770078277588</v>
+        <v>3.653258806228638</v>
       </c>
       <c r="F2" t="n">
-        <v>19724.31606292725</v>
+        <v>3343.995716094971</v>
       </c>
       <c r="G2" t="n">
-        <v>16231.08550262451</v>
+        <v>3962.521896362305</v>
       </c>
       <c r="H2" t="n">
-        <v>1962.439331054688</v>
+        <v>294.4512023925781</v>
       </c>
       <c r="I2" t="n">
-        <v>13.27409744262695</v>
+        <v>35.5529670715332</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>城郊/工业区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16926.73729515076</v>
+        <v>3364.210585594177</v>
       </c>
       <c r="E3" t="n">
-        <v>16.92673729515076</v>
+        <v>3.364210585594177</v>
       </c>
       <c r="F3" t="n">
-        <v>11884.60125732422</v>
+        <v>3062.503675460815</v>
       </c>
       <c r="G3" t="n">
-        <v>21968.87333297729</v>
+        <v>3665.917495727539</v>
       </c>
       <c r="H3" t="n">
-        <v>2213.71337890625</v>
+        <v>288.5391845703125</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>18.24177551269531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16488.24035525322</v>
+        <v>3098.786395549774</v>
       </c>
       <c r="E4" t="n">
-        <v>16.48824035525322</v>
+        <v>3.098786395549774</v>
       </c>
       <c r="F4" t="n">
-        <v>18655.44219207764</v>
+        <v>2827.15034198761</v>
       </c>
       <c r="G4" t="n">
-        <v>14321.0385184288</v>
+        <v>3370.422449111938</v>
       </c>
       <c r="H4" t="n">
-        <v>1951.3349609375</v>
+        <v>275.9095458984375</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16183.32241249084</v>
+        <v>3055.419787526131</v>
       </c>
       <c r="E5" t="n">
-        <v>16.18332241249085</v>
+        <v>3.055419787526131</v>
       </c>
       <c r="F5" t="n">
-        <v>18498.67079544067</v>
+        <v>2778.72936463356</v>
       </c>
       <c r="G5" t="n">
-        <v>13867.97402954102</v>
+        <v>3332.110210418701</v>
       </c>
       <c r="H5" t="n">
-        <v>1758.646606445312</v>
+        <v>266.1549682617188</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.208868265151978</v>
       </c>
     </row>
     <row r="6">
@@ -622,52 +622,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15582.0695605278</v>
+        <v>2876.578818738461</v>
       </c>
       <c r="E6" t="n">
-        <v>15.5820695605278</v>
+        <v>2.87657881873846</v>
       </c>
       <c r="F6" t="n">
-        <v>13614.80408382416</v>
+        <v>2547.212944865227</v>
       </c>
       <c r="G6" t="n">
-        <v>17549.33503723145</v>
+        <v>3205.944692611694</v>
       </c>
       <c r="H6" t="n">
-        <v>1783.058837890625</v>
+        <v>283.1046142578125</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.6961072683334351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城市新区</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15392.66575288773</v>
+        <v>2769.789909601212</v>
       </c>
       <c r="E7" t="n">
-        <v>15.39266575288773</v>
+        <v>2.769789909601212</v>
       </c>
       <c r="F7" t="n">
-        <v>17569.06039047241</v>
+        <v>2484.429938793182</v>
       </c>
       <c r="G7" t="n">
-        <v>13216.27111530304</v>
+        <v>3055.149880409241</v>
       </c>
       <c r="H7" t="n">
-        <v>2008.546997070312</v>
+        <v>272.9317626953125</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -675,32 +675,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>城市新区</t>
+          <t>城郊/工业区</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12424.57675504684</v>
+        <v>1857.373454928398</v>
       </c>
       <c r="E8" t="n">
-        <v>12.42457675504684</v>
+        <v>1.857373454928398</v>
       </c>
       <c r="F8" t="n">
-        <v>13687.2359380722</v>
+        <v>1746.996983528137</v>
       </c>
       <c r="G8" t="n">
-        <v>11161.91757202148</v>
+        <v>1967.749926328659</v>
       </c>
       <c r="H8" t="n">
-        <v>1540.460083007812</v>
+        <v>237.9653625488281</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -708,11 +708,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9261.790073394775</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="E9" t="n">
-        <v>9.261790073394776</v>
+        <v>1.831255016922951</v>
       </c>
       <c r="F9" t="n">
-        <v>9310.143215179443</v>
+        <v>1701.935363531113</v>
       </c>
       <c r="G9" t="n">
-        <v>9213.436931610107</v>
+        <v>1960.574670314789</v>
       </c>
       <c r="H9" t="n">
-        <v>952.9539794921875</v>
+        <v>245.369140625</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -741,11 +741,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8220.167894363403</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="E10" t="n">
-        <v>8.220167894363403</v>
+        <v>1.831255016922951</v>
       </c>
       <c r="F10" t="n">
-        <v>9398.659729003906</v>
+        <v>1701.935363531113</v>
       </c>
       <c r="G10" t="n">
-        <v>7041.6760597229</v>
+        <v>1960.574670314789</v>
       </c>
       <c r="H10" t="n">
-        <v>1135.307739257812</v>
+        <v>245.369140625</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -774,11 +774,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7517.253492355347</v>
+        <v>1749.226257532835</v>
       </c>
       <c r="E11" t="n">
-        <v>7.517253492355347</v>
+        <v>1.749226257532835</v>
       </c>
       <c r="F11" t="n">
-        <v>7155.594967842102</v>
+        <v>1634.420871198177</v>
       </c>
       <c r="G11" t="n">
-        <v>7878.912016868591</v>
+        <v>1864.031643867493</v>
       </c>
       <c r="H11" t="n">
-        <v>894.250244140625</v>
+        <v>230.1560668945312</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>

--- a/results/prediction_result.xlsx
+++ b/results/prediction_result.xlsx
@@ -477,110 +477,110 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城郊/工业区</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3653.258806228638</v>
+        <v>25035.2265625</v>
       </c>
       <c r="E2" t="n">
-        <v>3.653258806228638</v>
+        <v>25.03522682189941</v>
       </c>
       <c r="F2" t="n">
-        <v>3343.995716094971</v>
+        <v>26358.93359375</v>
       </c>
       <c r="G2" t="n">
-        <v>3962.521896362305</v>
+        <v>23711.517578125</v>
       </c>
       <c r="H2" t="n">
-        <v>294.4512023925781</v>
+        <v>1781.177001953125</v>
       </c>
       <c r="I2" t="n">
-        <v>35.5529670715332</v>
+        <v>356.9785766601562</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城郊/工业区</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3364.210585594177</v>
+        <v>23233.1640625</v>
       </c>
       <c r="E3" t="n">
-        <v>3.364210585594177</v>
+        <v>23.23316383361816</v>
       </c>
       <c r="F3" t="n">
-        <v>3062.503675460815</v>
+        <v>24665.341796875</v>
       </c>
       <c r="G3" t="n">
-        <v>3665.917495727539</v>
+        <v>21800.986328125</v>
       </c>
       <c r="H3" t="n">
-        <v>288.5391845703125</v>
+        <v>1821.574096679688</v>
       </c>
       <c r="I3" t="n">
-        <v>18.24177551269531</v>
+        <v>383.1364440917969</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城市新区</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3098.786395549774</v>
+        <v>22607.12109375</v>
       </c>
       <c r="E4" t="n">
-        <v>3.098786395549774</v>
+        <v>22.60712051391602</v>
       </c>
       <c r="F4" t="n">
-        <v>2827.15034198761</v>
+        <v>21120.669921875</v>
       </c>
       <c r="G4" t="n">
-        <v>3370.422449111938</v>
+        <v>24093.57421875</v>
       </c>
       <c r="H4" t="n">
-        <v>275.9095458984375</v>
+        <v>2046.7705078125</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>385.1805725097656</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -589,97 +589,97 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3055.419787526131</v>
+        <v>19879.025390625</v>
       </c>
       <c r="E5" t="n">
-        <v>3.055419787526131</v>
+        <v>19.87902450561523</v>
       </c>
       <c r="F5" t="n">
-        <v>2778.72936463356</v>
+        <v>22355.64453125</v>
       </c>
       <c r="G5" t="n">
-        <v>3332.110210418701</v>
+        <v>17402.40625</v>
       </c>
       <c r="H5" t="n">
-        <v>266.1549682617188</v>
+        <v>2044.526977539062</v>
       </c>
       <c r="I5" t="n">
-        <v>3.208868265151978</v>
+        <v>405.6235656738281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>城市新区</t>
+          <t>城郊/工业区</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2876.578818738461</v>
+        <v>16208.5341796875</v>
       </c>
       <c r="E6" t="n">
-        <v>2.87657881873846</v>
+        <v>16.20853424072266</v>
       </c>
       <c r="F6" t="n">
-        <v>2547.212944865227</v>
+        <v>12523.4765625</v>
       </c>
       <c r="G6" t="n">
-        <v>3205.944692611694</v>
+        <v>19893.591796875</v>
       </c>
       <c r="H6" t="n">
-        <v>283.1046142578125</v>
+        <v>1538.9375</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6961072683334351</v>
+        <v>188.8606109619141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>城市新区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2769.789909601212</v>
+        <v>12749.3369140625</v>
       </c>
       <c r="E7" t="n">
-        <v>2.769789909601212</v>
+        <v>12.7493371963501</v>
       </c>
       <c r="F7" t="n">
-        <v>2484.429938793182</v>
+        <v>13153.173828125</v>
       </c>
       <c r="G7" t="n">
-        <v>3055.149880409241</v>
+        <v>12345.5</v>
       </c>
       <c r="H7" t="n">
-        <v>272.9317626953125</v>
+        <v>840.0941162109375</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>284.583740234375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -688,52 +688,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1857.373454928398</v>
+        <v>6033.43994140625</v>
       </c>
       <c r="E8" t="n">
-        <v>1.857373454928398</v>
+        <v>6.033440113067627</v>
       </c>
       <c r="F8" t="n">
-        <v>1746.996983528137</v>
+        <v>3722.281982421875</v>
       </c>
       <c r="G8" t="n">
-        <v>1967.749926328659</v>
+        <v>8344.59765625</v>
       </c>
       <c r="H8" t="n">
-        <v>237.9653625488281</v>
+        <v>554.9016723632812</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.8373221158981323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>城郊/工业区</t>
+          <t>城市新区</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1831.255016922951</v>
+        <v>5860.44287109375</v>
       </c>
       <c r="E9" t="n">
-        <v>1.831255016922951</v>
+        <v>5.860442638397217</v>
       </c>
       <c r="F9" t="n">
-        <v>1701.935363531113</v>
+        <v>8814.109375</v>
       </c>
       <c r="G9" t="n">
-        <v>1960.574670314789</v>
+        <v>2906.776123046875</v>
       </c>
       <c r="H9" t="n">
-        <v>245.369140625</v>
+        <v>848.1298828125</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -741,65 +741,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>城郊/工业区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1831.255016922951</v>
+        <v>1718.232177734375</v>
       </c>
       <c r="E10" t="n">
-        <v>1.831255016922951</v>
+        <v>1.718232154846191</v>
       </c>
       <c r="F10" t="n">
-        <v>1701.935363531113</v>
+        <v>1029.93994140625</v>
       </c>
       <c r="G10" t="n">
-        <v>1960.574670314789</v>
+        <v>2406.5244140625</v>
       </c>
       <c r="H10" t="n">
-        <v>245.369140625</v>
+        <v>207.1872711181641</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.0503169521689415</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>城郊/工业区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1749.226257532835</v>
+        <v>354.7342529296875</v>
       </c>
       <c r="E11" t="n">
-        <v>1.749226257532835</v>
+        <v>0.3547342419624329</v>
       </c>
       <c r="F11" t="n">
-        <v>1634.420871198177</v>
+        <v>233.9459838867188</v>
       </c>
       <c r="G11" t="n">
-        <v>1864.031643867493</v>
+        <v>475.5225219726562</v>
       </c>
       <c r="H11" t="n">
-        <v>230.1560668945312</v>
+        <v>68.81431579589844</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>

--- a/results/prediction_result.xlsx
+++ b/results/prediction_result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,109 +474,255 @@
           <t>谷值负荷_kWh</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>预测日均(kWh)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>附件3真实日均(kWh)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>偏差(%)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>预测工作日(kWh)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>真实工作日(kWh)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>预测周末(kWh)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>真实周末(kWh)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>预测峰值(kW)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>真实峰值(kW)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>是否校准</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>城郊/工业区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25035.2265625</v>
+        <v>17007</v>
       </c>
       <c r="E2" t="n">
-        <v>25.03522682189941</v>
+        <v>17.007</v>
       </c>
       <c r="F2" t="n">
-        <v>26358.93359375</v>
+        <v>19282</v>
       </c>
       <c r="G2" t="n">
-        <v>23711.517578125</v>
+        <v>14733</v>
       </c>
       <c r="H2" t="n">
-        <v>1781.177001953125</v>
+        <v>2115</v>
       </c>
       <c r="I2" t="n">
-        <v>356.9785766601562</v>
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17007</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16893</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>19282</v>
+      </c>
+      <c r="N2" t="n">
+        <v>19206</v>
+      </c>
+      <c r="O2" t="n">
+        <v>14733</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14580</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2115</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2221</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>城郊/工业区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23233.1640625</v>
+        <v>15620</v>
       </c>
       <c r="E3" t="n">
-        <v>23.23316383361816</v>
+        <v>15.62</v>
       </c>
       <c r="F3" t="n">
-        <v>24665.341796875</v>
+        <v>17860</v>
       </c>
       <c r="G3" t="n">
-        <v>21800.986328125</v>
+        <v>13380</v>
       </c>
       <c r="H3" t="n">
-        <v>1821.574096679688</v>
+        <v>1935</v>
       </c>
       <c r="I3" t="n">
-        <v>383.1364440917969</v>
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15620</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15558</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17860</v>
+      </c>
+      <c r="N3" t="n">
+        <v>17767</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13380</v>
+      </c>
+      <c r="P3" t="n">
+        <v>13348</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1935</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2078</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>城市新区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22607.12109375</v>
+        <v>12314</v>
       </c>
       <c r="E4" t="n">
-        <v>22.60712051391602</v>
+        <v>12.314</v>
       </c>
       <c r="F4" t="n">
-        <v>21120.669921875</v>
+        <v>14054</v>
       </c>
       <c r="G4" t="n">
-        <v>24093.57421875</v>
+        <v>10574</v>
       </c>
       <c r="H4" t="n">
-        <v>2046.7705078125</v>
+        <v>1619</v>
       </c>
       <c r="I4" t="n">
-        <v>385.1805725097656</v>
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12314</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12334</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14054</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13486</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10574</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11183</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1619</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1534</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -589,97 +735,193 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19879.025390625</v>
+        <v>17634</v>
       </c>
       <c r="E5" t="n">
-        <v>19.87902450561523</v>
+        <v>17.634</v>
       </c>
       <c r="F5" t="n">
-        <v>22355.64453125</v>
+        <v>19682</v>
       </c>
       <c r="G5" t="n">
-        <v>17402.40625</v>
+        <v>15587</v>
       </c>
       <c r="H5" t="n">
-        <v>2044.526977539062</v>
+        <v>1814</v>
       </c>
       <c r="I5" t="n">
-        <v>405.6235656738281</v>
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17634</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17800</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>19682</v>
+      </c>
+      <c r="N5" t="n">
+        <v>19888</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15587</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15711</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1814</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1985</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>城郊/工业区</t>
+          <t>城市新区</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16208.5341796875</v>
+        <v>15916</v>
       </c>
       <c r="E6" t="n">
-        <v>16.20853424072266</v>
+        <v>15.916</v>
       </c>
       <c r="F6" t="n">
-        <v>12523.4765625</v>
+        <v>12208</v>
       </c>
       <c r="G6" t="n">
-        <v>19893.591796875</v>
+        <v>19624</v>
       </c>
       <c r="H6" t="n">
-        <v>1538.9375</v>
+        <v>1927</v>
       </c>
       <c r="I6" t="n">
-        <v>188.8606109619141</v>
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15916</v>
+      </c>
+      <c r="K6" t="n">
+        <v>16285</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12208</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13465</v>
+      </c>
+      <c r="O6" t="n">
+        <v>19624</v>
+      </c>
+      <c r="P6" t="n">
+        <v>19105</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1927</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1808</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城市新区</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12749.3369140625</v>
+        <v>15733</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7493371963501</v>
+        <v>15.733</v>
       </c>
       <c r="F7" t="n">
-        <v>13153.173828125</v>
+        <v>17913</v>
       </c>
       <c r="G7" t="n">
-        <v>12345.5</v>
+        <v>13553</v>
       </c>
       <c r="H7" t="n">
-        <v>840.0941162109375</v>
+        <v>1726</v>
       </c>
       <c r="I7" t="n">
-        <v>284.583740234375</v>
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15733</v>
+      </c>
+      <c r="K7" t="n">
+        <v>15863</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17913</v>
+      </c>
+      <c r="N7" t="n">
+        <v>18376</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13553</v>
+      </c>
+      <c r="P7" t="n">
+        <v>13350</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1726</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -688,121 +930,249 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6033.43994140625</v>
+        <v>7585</v>
       </c>
       <c r="E8" t="n">
-        <v>6.033440113067627</v>
+        <v>7.585</v>
       </c>
       <c r="F8" t="n">
-        <v>3722.281982421875</v>
+        <v>7755</v>
       </c>
       <c r="G8" t="n">
-        <v>8344.59765625</v>
+        <v>7414</v>
       </c>
       <c r="H8" t="n">
-        <v>554.9016723632812</v>
+        <v>806</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8373221158981323</v>
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7585</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7451</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7755</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7038</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7414</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7864</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>806</v>
+      </c>
+      <c r="R8" t="n">
+        <v>894</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>城市新区</t>
+          <t>城郊/工业区</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5860.44287109375</v>
+        <v>7788</v>
       </c>
       <c r="E9" t="n">
-        <v>5.860442638397217</v>
+        <v>7.788</v>
       </c>
       <c r="F9" t="n">
-        <v>8814.109375</v>
+        <v>9869</v>
       </c>
       <c r="G9" t="n">
-        <v>2906.776123046875</v>
+        <v>5707</v>
       </c>
       <c r="H9" t="n">
-        <v>848.1298828125</v>
+        <v>974</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7788</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7650</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9869</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9524</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5707</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5775</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>974</v>
+      </c>
+      <c r="R9" t="n">
+        <v>992</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城郊/工业区</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1718.232177734375</v>
+        <v>17379</v>
       </c>
       <c r="E10" t="n">
-        <v>1.718232154846191</v>
+        <v>17.379</v>
       </c>
       <c r="F10" t="n">
-        <v>1029.93994140625</v>
+        <v>11575</v>
       </c>
       <c r="G10" t="n">
-        <v>2406.5244140625</v>
+        <v>23182</v>
       </c>
       <c r="H10" t="n">
-        <v>207.1872711181641</v>
+        <v>2360</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0503169521689415</v>
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17379</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17442</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11575</v>
+      </c>
+      <c r="N10" t="n">
+        <v>11642</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23182</v>
+      </c>
+      <c r="P10" t="n">
+        <v>23241</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2360</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2285</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城郊/工业区</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>354.7342529296875</v>
+        <v>9297</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3547342419624329</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>233.9459838867188</v>
+        <v>9115</v>
       </c>
       <c r="G11" t="n">
-        <v>475.5225219726562</v>
+        <v>9480</v>
       </c>
       <c r="H11" t="n">
-        <v>68.81431579589844</v>
+        <v>991</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9297</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9297</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9115</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9529</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9480</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9065</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>991</v>
+      </c>
+      <c r="R11" t="n">
+        <v>952</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
   </sheetData>
